--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Update formula_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Update formula_report.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="153222"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitRepos\GroupDocs.Assembly-for-Java\Examples\GroupDocs.Assembly.Examples.Java\Data\Storage\Spreadsheet Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -126,7 +131,7 @@
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -141,25 +146,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -167,25 +158,29 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="5"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -529,11 +524,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:B26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="65.57142857142857" customWidth="1"/>
+    <col min="1" max="1" width="65.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
@@ -661,7 +656,7 @@
         <v>7</v>
       </c>
       <c r="B24">
-        <v>11000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15">
@@ -669,7 +664,8 @@
         <v>8</v>
       </c>
       <c r="B25">
-        <v>27500</v>
+        <f>SUM(B23:B24)</f>
+        <v>19500</v>
       </c>
     </row>
   </sheetData>
